--- a/artfynd/A 40023-2019 artfynd.xlsx
+++ b/artfynd/A 40023-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1514,6 +1514,132 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>63181549</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56133</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Barbastella barbastellus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kvilla, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>558086</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6254769</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2014-07-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2014-07-31</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40023-2019 artfynd.xlsx
+++ b/artfynd/A 40023-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
